--- a/kawasaki_project/05_試算・管理シート/川崎町_交付金_取りまとめ表_R8.9.29.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_交付金_取りまとめ表_R8.9.29.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3か年の枝番（ア・イ・ウ…）を突き合わせ、各年度の枝番の合計が公表されている合計得点（454点・565点・528点）と一致することを確認している。</t>
+          <t>3か年の枝番（ア・イ・ウ…）を突き合わせ、各年度の枝番の合計と公表されている合計得点（454点・565点・528点）を照合した。令和7年度（565点）・令和8年度（528点）は一致する。⚠ 令和6年度は枝番の合計が428点であり、公表値454点と26点食い違う。本表は令和8年度の評価指標の枝番の一覧を軸にしているため、令和6年度にあって令和8年度にない枝番（体制・取組指標群26点）が本表に含まれていないことによる。令和6年度の指標群別の得点は、原典（01_（掲載用）令和６年度評価結果）の指標群別の列により、体制・取組366点・活動58点・成果30点＝454点であることを確かめている（計画素案の図3-1はこの原典の値による）。</t>
         </is>
       </c>
     </row>
